--- a/gold_commitment_master_comparison.xlsx
+++ b/gold_commitment_master_comparison.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'gold_and_annotators'!$A$1:$AD$140</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'model_predictions'!$A$1:$P$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'model_predictions'!$A$1:$S$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'commitment_disagreements'!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'legend'!$A$1:$B$13</definedName>
   </definedNames>
@@ -17684,7 +17684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P140"/>
+  <dimension ref="A1:S140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17703,6 +17703,9 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -17773,15 +17776,30 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>gemma4_31b_it_pred</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>gemma4_31b_it_ok</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>gemma4_31b_it_pNC</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>gemini_3.1_pro_pred</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>gemini_3.1_pro_ok</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>gemini_3.1_pro_pNC</t>
         </is>
@@ -17860,6 +17878,19 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17934,6 +17965,19 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18008,6 +18052,19 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18071,17 +18128,30 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18156,6 +18226,19 @@
       <c r="P6" t="n">
         <v>1</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18219,15 +18302,28 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>insufficient_data</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -18293,15 +18389,28 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>claim_false</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -18378,6 +18487,19 @@
       <c r="P9" t="n">
         <v>0</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18441,17 +18563,30 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18515,15 +18650,28 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>none_clear</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -18589,15 +18737,28 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>supportive</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18663,15 +18824,28 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>unsupportive</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18748,6 +18922,19 @@
       <c r="P14" t="n">
         <v>1</v>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18820,6 +19007,19 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18896,6 +19096,19 @@
       <c r="P16" t="n">
         <v>0.5</v>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>unsupportive</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18959,15 +19172,28 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>supportive</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="S17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19031,9 +19257,22 @@
       <c r="M18" t="n">
         <v>0.05</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19095,9 +19334,22 @@
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -19159,9 +19411,22 @@
       <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19223,9 +19488,22 @@
       <c r="M21" t="n">
         <v>0.1</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>sound</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19287,9 +19565,22 @@
       <c r="M22" t="n">
         <v>0.1</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19351,9 +19642,22 @@
       <c r="M23" t="n">
         <v>0.1</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>claim_true</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19415,9 +19719,22 @@
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19479,9 +19796,22 @@
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19543,9 +19873,22 @@
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19607,9 +19950,22 @@
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19671,9 +20027,22 @@
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>claim_true</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19735,9 +20104,22 @@
       <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19799,9 +20181,22 @@
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>growth</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19863,9 +20258,22 @@
       <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -19927,9 +20335,22 @@
       <c r="M32" t="n">
         <v>0.05</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>claim_true</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -19991,9 +20412,22 @@
       <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -20055,9 +20489,22 @@
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -20119,9 +20566,22 @@
       <c r="M35" t="n">
         <v>0.85</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -20183,9 +20643,22 @@
       <c r="M36" t="n">
         <v>0.95</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20247,9 +20720,22 @@
       <c r="M37" t="n">
         <v>0.35</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20311,9 +20797,22 @@
       <c r="M38" t="n">
         <v>0.05</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20375,9 +20874,22 @@
       <c r="M39" t="n">
         <v>0.95</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20439,9 +20951,22 @@
       <c r="M40" t="n">
         <v>0.1</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>claim_true</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -20503,9 +21028,22 @@
       <c r="M41" t="n">
         <v>0.05</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -20567,9 +21105,22 @@
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -20631,9 +21182,22 @@
       <c r="M43" t="n">
         <v>1</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -20695,9 +21259,22 @@
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -20759,9 +21336,22 @@
       <c r="M45" t="n">
         <v>0.9</v>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20823,9 +21413,22 @@
       <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -20887,9 +21490,22 @@
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>KHC</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -20951,9 +21567,22 @@
       <c r="M48" t="n">
         <v>0.1</v>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -21015,9 +21644,22 @@
       <c r="M49" t="n">
         <v>0.1</v>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -21079,9 +21721,22 @@
       <c r="M50" t="n">
         <v>1</v>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -21143,9 +21798,22 @@
       <c r="M51" t="n">
         <v>1</v>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -21207,9 +21875,22 @@
       <c r="M52" t="n">
         <v>0</v>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>premise_false</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -21271,9 +21952,22 @@
       <c r="M53" t="n">
         <v>1</v>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -21335,9 +22029,22 @@
       <c r="M54" t="n">
         <v>0</v>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -21399,9 +22106,22 @@
       <c r="M55" t="n">
         <v>0</v>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -21463,9 +22183,22 @@
       <c r="M56" t="n">
         <v>0.05</v>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -21527,9 +22260,22 @@
       <c r="M57" t="n">
         <v>0</v>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -21591,9 +22337,22 @@
       <c r="M58" t="n">
         <v>0.9</v>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -21655,9 +22414,22 @@
       <c r="M59" t="n">
         <v>0.7</v>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -21719,9 +22491,22 @@
       <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>unsupportive</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -21783,9 +22568,22 @@
       <c r="M61" t="n">
         <v>1</v>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -21847,9 +22645,22 @@
       <c r="M62" t="n">
         <v>0.6</v>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>take_profits</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -21911,9 +22722,22 @@
       <c r="M63" t="n">
         <v>1</v>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -21975,9 +22799,22 @@
       <c r="M64" t="n">
         <v>1</v>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -22039,9 +22876,22 @@
       <c r="M65" t="n">
         <v>0.75</v>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -22103,9 +22953,22 @@
       <c r="M66" t="n">
         <v>1</v>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22167,9 +23030,22 @@
       <c r="M67" t="n">
         <v>1</v>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -22231,9 +23107,22 @@
       <c r="M68" t="n">
         <v>0.05</v>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -22295,9 +23184,22 @@
       <c r="M69" t="n">
         <v>1</v>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -22359,9 +23261,22 @@
       <c r="M70" t="n">
         <v>1</v>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -22423,9 +23338,22 @@
       <c r="M71" t="n">
         <v>1</v>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -22487,9 +23415,22 @@
       <c r="M72" t="n">
         <v>1</v>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -22551,9 +23492,22 @@
       <c r="M73" t="n">
         <v>0.95</v>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -22615,9 +23569,22 @@
       <c r="M74" t="n">
         <v>0</v>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>aligned</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -22679,9 +23646,22 @@
       <c r="M75" t="n">
         <v>0.75</v>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -22743,9 +23723,22 @@
       <c r="M76" t="n">
         <v>0.5</v>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -22807,9 +23800,22 @@
       <c r="M77" t="n">
         <v>0.55</v>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -22871,9 +23877,22 @@
       <c r="M78" t="n">
         <v>1</v>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -22935,9 +23954,22 @@
       <c r="M79" t="n">
         <v>0.95</v>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -22999,9 +24031,22 @@
       <c r="M80" t="n">
         <v>0.85</v>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -23063,9 +24108,22 @@
       <c r="M81" t="n">
         <v>0.7</v>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>claim_true</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -23127,9 +24185,22 @@
       <c r="M82" t="n">
         <v>0.95</v>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -23191,9 +24262,22 @@
       <c r="M83" t="n">
         <v>0.8</v>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -23255,9 +24339,22 @@
       <c r="M84" t="n">
         <v>1</v>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -23319,9 +24416,22 @@
       <c r="M85" t="n">
         <v>0.75</v>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -23383,9 +24493,22 @@
       <c r="M86" t="n">
         <v>0.8</v>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -23447,9 +24570,22 @@
       <c r="M87" t="n">
         <v>0.95</v>
       </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -23511,9 +24647,22 @@
       <c r="M88" t="n">
         <v>0.7</v>
       </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -23575,9 +24724,22 @@
       <c r="M89" t="n">
         <v>0.4</v>
       </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>reinvestment_opportunity</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -23639,9 +24801,22 @@
       <c r="M90" t="n">
         <v>1</v>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -23703,9 +24878,22 @@
       <c r="M91" t="n">
         <v>1</v>
       </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -23767,9 +24955,22 @@
       <c r="M92" t="n">
         <v>0.9</v>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -23831,9 +25032,22 @@
       <c r="M93" t="n">
         <v>0.2</v>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>value_trap</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -23895,9 +25109,22 @@
       <c r="M94" t="n">
         <v>0.75</v>
       </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -23959,9 +25186,22 @@
       <c r="M95" t="n">
         <v>0</v>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -24023,9 +25263,22 @@
       <c r="M96" t="n">
         <v>0.8</v>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -24087,9 +25340,22 @@
       <c r="M97" t="n">
         <v>0.65</v>
       </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -24151,9 +25417,22 @@
       <c r="M98" t="n">
         <v>0.25</v>
       </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -24215,9 +25494,22 @@
       <c r="M99" t="n">
         <v>1</v>
       </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -24279,9 +25571,22 @@
       <c r="M100" t="n">
         <v>1</v>
       </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -24343,9 +25648,22 @@
       <c r="M101" t="n">
         <v>1</v>
       </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -24407,9 +25725,22 @@
       <c r="M102" t="n">
         <v>0.4</v>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -24471,9 +25802,22 @@
       <c r="M103" t="n">
         <v>1</v>
       </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>insufficient_data</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -24535,9 +25879,22 @@
       <c r="M104" t="n">
         <v>0</v>
       </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEHC</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -24599,9 +25956,22 @@
       <c r="M105" t="n">
         <v>0</v>
       </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -24663,9 +26033,22 @@
       <c r="M106" t="n">
         <v>0</v>
       </c>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -24727,9 +26110,22 @@
       <c r="M107" t="n">
         <v>0</v>
       </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -24791,9 +26187,22 @@
       <c r="M108" t="n">
         <v>0.025</v>
       </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -24855,9 +26264,22 @@
       <c r="M109" t="n">
         <v>0</v>
       </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -24919,9 +26341,22 @@
       <c r="M110" t="n">
         <v>0</v>
       </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -24983,9 +26418,22 @@
       <c r="M111" t="n">
         <v>0</v>
       </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -25047,9 +26495,22 @@
       <c r="M112" t="n">
         <v>0</v>
       </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -25111,9 +26572,22 @@
       <c r="M113" t="n">
         <v>0</v>
       </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -25175,9 +26649,22 @@
       <c r="M114" t="n">
         <v>1</v>
       </c>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>none_clear</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -25239,9 +26726,22 @@
       <c r="M115" t="n">
         <v>0</v>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>none_clear</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -25303,9 +26803,22 @@
       <c r="M116" t="n">
         <v>0</v>
       </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -25367,9 +26880,22 @@
       <c r="M117" t="n">
         <v>0</v>
       </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -25431,9 +26957,22 @@
       <c r="M118" t="n">
         <v>0</v>
       </c>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -25495,9 +27034,22 @@
       <c r="M119" t="n">
         <v>0</v>
       </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -25559,9 +27111,22 @@
       <c r="M120" t="n">
         <v>0</v>
       </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -25623,9 +27188,22 @@
       <c r="M121" t="n">
         <v>0</v>
       </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -25687,9 +27265,22 @@
       <c r="M122" t="n">
         <v>0.05</v>
       </c>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>CPRT</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -25751,9 +27342,22 @@
       <c r="M123" t="n">
         <v>0</v>
       </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -25815,9 +27419,22 @@
       <c r="M124" t="n">
         <v>0</v>
       </c>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>TTD</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -25879,9 +27496,22 @@
       <c r="M125" t="n">
         <v>0</v>
       </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -25943,9 +27573,22 @@
       <c r="M126" t="n">
         <v>0</v>
       </c>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -26007,9 +27650,22 @@
       <c r="M127" t="n">
         <v>0.925</v>
       </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>none_clear</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -26071,9 +27727,22 @@
       <c r="M128" t="n">
         <v>0</v>
       </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -26135,9 +27804,22 @@
       <c r="M129" t="n">
         <v>0.125</v>
       </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -26199,9 +27881,22 @@
       <c r="M130" t="n">
         <v>0</v>
       </c>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -26263,9 +27958,22 @@
       <c r="M131" t="n">
         <v>0.025</v>
       </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -26327,9 +28035,22 @@
       <c r="M132" t="n">
         <v>0</v>
       </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -26391,9 +28112,22 @@
       <c r="M133" t="n">
         <v>0</v>
       </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -26455,9 +28189,22 @@
       <c r="M134" t="n">
         <v>0</v>
       </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -26519,9 +28266,22 @@
       <c r="M135" t="n">
         <v>0</v>
       </c>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -26583,9 +28343,22 @@
       <c r="M136" t="n">
         <v>0</v>
       </c>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -26647,9 +28420,22 @@
       <c r="M137" t="n">
         <v>0</v>
       </c>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -26711,9 +28497,22 @@
       <c r="M138" t="n">
         <v>0</v>
       </c>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -26775,9 +28574,22 @@
       <c r="M139" t="n">
         <v>0</v>
       </c>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -26839,12 +28651,25 @@
       <c r="M140" t="n">
         <v>0</v>
       </c>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P140"/>
+  <autoFilter ref="A1:S140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
